--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -508,7 +508,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1155,7 +1155,7 @@
     <t>実行される調剤イベントのタイプを示す。たとえば、トライアルフィル、トライアルの完了、部分フィル、緊急フィル、サンプルなどである。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -1304,7 +1304,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
